--- a/site/American-Express-Work-Okta-Integration-Guide/headings.xlsx
+++ b/site/American-Express-Work-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,29 +925,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KNS19F76NZ0CHY1F20BPJHX6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01KNS19F76NZ0CHY1F20BPJHX6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,54 +979,76 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/American-Express-Work-Okta-Integration-Guide/headings.xlsx
+++ b/site/American-Express-Work-Okta-Integration-Guide/headings.xlsx
@@ -935,12 +935,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KNS19F76NZ0CHY1F20BPJHX6</t>
+          <t>h_01KNTTBWZ3QW9Z7ZXZR61QKFV1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01KNS19F76NZ0CHY1F20BPJHX6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01KNTTBWZ3QW9Z7ZXZR61QKFV1</t>
         </is>
       </c>
     </row>

--- a/site/American-Express-Work-Okta-Integration-Guide/headings.xlsx
+++ b/site/American-Express-Work-Okta-Integration-Guide/headings.xlsx
@@ -935,12 +935,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KNTTBWZ3QW9Z7ZXZR61QKFV1</t>
+          <t>h_01KNTWBY9KNQNKZMJXEVSAYMF5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01KNTTBWZ3QW9Z7ZXZR61QKFV1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01KNTWBY9KNQNKZMJXEVSAYMF5</t>
         </is>
       </c>
     </row>

--- a/site/American-Express-Work-Okta-Integration-Guide/headings.xlsx
+++ b/site/American-Express-Work-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -947,51 +947,51 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>User Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KP31N9ZWMZP49BPQ83TFSTEH</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01KP31N9ZWMZP49BPQ83TFSTEH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Card Application Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01KP31N9ZW6NH1PHQA2CZX6QJT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01KP31N9ZW6NH1PHQA2CZX6QJT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,54 +1001,98 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Work-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
